--- a/Schematic/shield-BOM.xlsx
+++ b/Schematic/shield-BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Documents\Altium\Projects\ESP32DIV2-Shield\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Github\ESP32-DIV\Schematic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12F7C05A-9F33-4AA6-852B-8B02B5ECB7B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252CC9B3-6554-4B69-B246-6586CBA09FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{24138C6C-8319-4465-AB62-3EA080267F84}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24138C6C-8319-4465-AB62-3EA080267F84}"/>
   </bookViews>
   <sheets>
     <sheet name="shield-BOM" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="57">
   <si>
     <t>Comment</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>CC1101_M_SMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANT U.FL </t>
   </si>
 </sst>
 </file>
@@ -643,7 +646,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
